--- a/TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
+++ b/TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nykgroup-my.sharepoint.com/personal/nguyenbich_ngoc_nykgroup_com/Documents/CS standard time/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nykgroup-my.sharepoint.com/personal/nguyenbich_ngoc_nykgroup_com/Documents/CS standard time_Claude/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="965" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{777AE143-F3B3-4D71-8A26-BBB87E68F491}"/>
+  <xr:revisionPtr revIDLastSave="985" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D2C4F31-FA0F-4217-8291-878E0A1E0CE8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="745" xr2:uid="{E21F554E-3F05-4DDC-8BE4-80952248A30F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="745" activeTab="1" xr2:uid="{E21F554E-3F05-4DDC-8BE4-80952248A30F}"/>
   </bookViews>
   <sheets>
     <sheet name="HC" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
     <sheet name="E" sheetId="14" r:id="rId13"/>
     <sheet name="Ghi chú" sheetId="20" r:id="rId14"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'C'!$A$2:$O$75</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -52,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="530">
   <si>
     <t>Total</t>
   </si>
@@ -988,21 +991,676 @@
   </si>
   <si>
     <t>1 FTE/tháng = 8 giờ × 95% × 22 ngày = 167.2 giờ/tháng = 10,032 phút/tháng.</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>AIR IMPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIR EXPORT </t>
+  </si>
+  <si>
+    <t>SEA IMPORT</t>
+  </si>
+  <si>
+    <t>DOMESTIC IMPORT</t>
+  </si>
+  <si>
+    <t>DOMESTIC EXPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> INLAND FROM POINT A TO POINT B ONLY </t>
+  </si>
+  <si>
+    <t>CROSSBORDER EXPORT</t>
+  </si>
+  <si>
+    <t>CROSSBORDER  IMPORT</t>
+  </si>
+  <si>
+    <t>HANDCARRY EXPORT</t>
+  </si>
+  <si>
+    <t>HANDCARRY IMPORT</t>
+  </si>
+  <si>
+    <t>RAIL EXPORT</t>
+  </si>
+  <si>
+    <t>RAIL IMPORT</t>
+  </si>
+  <si>
+    <t>RAIL DOMESTIC</t>
+  </si>
+  <si>
+    <t>Scope of Job</t>
+  </si>
+  <si>
+    <t>CTAW</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Air + B.Warehouse</t>
+  </si>
+  <si>
+    <t>CTOW</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Ocean + B.Warehouse</t>
+  </si>
+  <si>
+    <t>CTOB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Ocean</t>
+  </si>
+  <si>
+    <t>CTAB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Air</t>
+  </si>
+  <si>
+    <t>CTWB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking +B. Warehouse</t>
+  </si>
+  <si>
+    <t>CTRB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Rail</t>
+  </si>
+  <si>
+    <t>CAWB</t>
+  </si>
+  <si>
+    <t>Customs + Air + B.Warehouse</t>
+  </si>
+  <si>
+    <t>COWB</t>
+  </si>
+  <si>
+    <t>Customs + Ocean + B.Warehouse</t>
+  </si>
+  <si>
+    <t>CTBB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking</t>
+  </si>
+  <si>
+    <t>CWBB</t>
+  </si>
+  <si>
+    <t>Customs +B. Warehouse</t>
+  </si>
+  <si>
+    <t>COBB</t>
+  </si>
+  <si>
+    <t>Customs + Ocean</t>
+  </si>
+  <si>
+    <t>CABB</t>
+  </si>
+  <si>
+    <t>Customs + Air</t>
+  </si>
+  <si>
+    <t>CTCR</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Cross-Border Rail</t>
+  </si>
+  <si>
+    <t>CRBB</t>
+  </si>
+  <si>
+    <t>Customs + Rail</t>
+  </si>
+  <si>
+    <t>CARB</t>
+  </si>
+  <si>
+    <t>Customs + Air + Rail</t>
+  </si>
+  <si>
+    <t>CWRB</t>
+  </si>
+  <si>
+    <t>Customs + B.Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>CORB</t>
+  </si>
+  <si>
+    <t>Customs + Ocean + Rail</t>
+  </si>
+  <si>
+    <t>COWR</t>
+  </si>
+  <si>
+    <t>Customs + Ocean + B.Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>TAWB</t>
+  </si>
+  <si>
+    <t>Trucking + Air + B.Warehouse</t>
+  </si>
+  <si>
+    <t>TOBB</t>
+  </si>
+  <si>
+    <t>Trucking + Ocean</t>
+  </si>
+  <si>
+    <t>TOWB</t>
+  </si>
+  <si>
+    <t>Trucking + Ocean +B.Warehouse</t>
+  </si>
+  <si>
+    <t>TABB</t>
+  </si>
+  <si>
+    <t>Trucking + Air</t>
+  </si>
+  <si>
+    <t>TBBB</t>
+  </si>
+  <si>
+    <t>Trucking Only</t>
+  </si>
+  <si>
+    <t>TWBB</t>
+  </si>
+  <si>
+    <t>Trucking +B.Warehouse</t>
+  </si>
+  <si>
+    <t>TRBB</t>
+  </si>
+  <si>
+    <t>Trucking + Rail</t>
+  </si>
+  <si>
+    <t>TAOB</t>
+  </si>
+  <si>
+    <t>Trucking + Air + Ocean</t>
+  </si>
+  <si>
+    <t>TARB</t>
+  </si>
+  <si>
+    <t>Trucking + Air + Rail</t>
+  </si>
+  <si>
+    <t>TORB</t>
+  </si>
+  <si>
+    <t>Trucking + Ocean + Rail</t>
+  </si>
+  <si>
+    <t>TWRB</t>
+  </si>
+  <si>
+    <t>Trucking +B.Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>UBBB</t>
+  </si>
+  <si>
+    <t>Trucking Round-Use</t>
+  </si>
+  <si>
+    <t>MBBB</t>
+  </si>
+  <si>
+    <t>Trucking Milkrun/Shuttle</t>
+  </si>
+  <si>
+    <t>ABBB</t>
+  </si>
+  <si>
+    <t>Air Freight Only</t>
+  </si>
+  <si>
+    <t>OBBB</t>
+  </si>
+  <si>
+    <t>Ocean Freight Only</t>
+  </si>
+  <si>
+    <t>WBBB</t>
+  </si>
+  <si>
+    <t>B.Warehouse Only</t>
+  </si>
+  <si>
+    <t>RBBB</t>
+  </si>
+  <si>
+    <t>Rail Only</t>
+  </si>
+  <si>
+    <t>AWBB</t>
+  </si>
+  <si>
+    <t>Air + B.Warehouse</t>
+  </si>
+  <si>
+    <t>OWBB</t>
+  </si>
+  <si>
+    <t>Ocean +B. Warehouse</t>
+  </si>
+  <si>
+    <t>ARBB</t>
+  </si>
+  <si>
+    <t>Air + Rail</t>
+  </si>
+  <si>
+    <t>ORBB</t>
+  </si>
+  <si>
+    <t>Ocean + Rail</t>
+  </si>
+  <si>
+    <t>WRBB</t>
+  </si>
+  <si>
+    <t>B.Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>AWRB</t>
+  </si>
+  <si>
+    <t>Air + B.Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>OWRB</t>
+  </si>
+  <si>
+    <t>Ocean +B. Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>CBTB</t>
+  </si>
+  <si>
+    <t>Cross-Border Truck</t>
+  </si>
+  <si>
+    <t>CBTW</t>
+  </si>
+  <si>
+    <t>Cross-Border + B.Warehouse</t>
+  </si>
+  <si>
+    <t>CBTA</t>
+  </si>
+  <si>
+    <t>Cross-Border Truck + Air</t>
+  </si>
+  <si>
+    <t>CBTO</t>
+  </si>
+  <si>
+    <t>Cross-Border + Ocean</t>
+  </si>
+  <si>
+    <t>CBRB</t>
+  </si>
+  <si>
+    <t>Cross-Border Rail</t>
+  </si>
+  <si>
+    <t>BCLC</t>
+  </si>
+  <si>
+    <t>Buyer Consol (Cross-Border Truck/Rail)</t>
+  </si>
+  <si>
+    <t>BCLO</t>
+  </si>
+  <si>
+    <t>Buyer Consol (Ocean)</t>
+  </si>
+  <si>
+    <t>APRB</t>
+  </si>
+  <si>
+    <t>Air Charter</t>
+  </si>
+  <si>
+    <t>CBBB</t>
+  </si>
+  <si>
+    <t>Customs Only</t>
+  </si>
+  <si>
+    <t>BBBB</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>IBBB</t>
+  </si>
+  <si>
+    <t>Trouble-shooting Handling</t>
+  </si>
+  <si>
+    <t>FCTB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + Truck</t>
+  </si>
+  <si>
+    <t>FTBB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Truck</t>
+  </si>
+  <si>
+    <t>FCBB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs</t>
+  </si>
+  <si>
+    <t>FWBB</t>
+  </si>
+  <si>
+    <t>Booking Agent +B. Warehouse</t>
+  </si>
+  <si>
+    <t>FTWB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Truck +B. Warehouse</t>
+  </si>
+  <si>
+    <t>FCWB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs +B. Warehouse</t>
+  </si>
+  <si>
+    <t>FCTW</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + Truck +B. Warehouse</t>
+  </si>
+  <si>
+    <t>FBBB</t>
+  </si>
+  <si>
+    <t>Booking Agent</t>
+  </si>
+  <si>
+    <t>VBBB</t>
+  </si>
+  <si>
+    <t>Vendor Booking Release</t>
+  </si>
+  <si>
+    <t>DBBB</t>
+  </si>
+  <si>
+    <t>Vendor Doc</t>
+  </si>
+  <si>
+    <t>CTAS</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Air + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CTOS</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Ocean + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CTSB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CASB</t>
+  </si>
+  <si>
+    <t>Customs + Air + CFS warehouse</t>
+  </si>
+  <si>
+    <t>COSB</t>
+  </si>
+  <si>
+    <t>Customs + Ocean + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CSBB</t>
+  </si>
+  <si>
+    <t>Customs + CFS warehouse</t>
+  </si>
+  <si>
+    <t>TASB</t>
+  </si>
+  <si>
+    <t>Trucking + Air + CFS warehouse</t>
+  </si>
+  <si>
+    <t>TOSB</t>
+  </si>
+  <si>
+    <t>Trucking + Ocean + CFS warehouse</t>
+  </si>
+  <si>
+    <t>TSBB</t>
+  </si>
+  <si>
+    <t>Trucking + CFS warehouse</t>
+  </si>
+  <si>
+    <t>SBBB</t>
+  </si>
+  <si>
+    <t>CFS warehouse Only</t>
+  </si>
+  <si>
+    <t>ASBB</t>
+  </si>
+  <si>
+    <t>Air + CFS warehouse</t>
+  </si>
+  <si>
+    <t>OSBB</t>
+  </si>
+  <si>
+    <t>Ocean + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CBTS</t>
+  </si>
+  <si>
+    <t>Cross-Border + CFS warehouse</t>
+  </si>
+  <si>
+    <t>FSBB</t>
+  </si>
+  <si>
+    <t>Booking Agent + CFS warehouse</t>
+  </si>
+  <si>
+    <t>FTSB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Truck + CFS warehouse</t>
+  </si>
+  <si>
+    <t>FCSB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + CFS warehouse</t>
+  </si>
+  <si>
+    <t>FCTS</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + Truck + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CTAG</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Air + General warehouse</t>
+  </si>
+  <si>
+    <t>CTOG</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Ocean + General warehouse</t>
+  </si>
+  <si>
+    <t>CTGB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + General warehouse</t>
+  </si>
+  <si>
+    <t>CAGB</t>
+  </si>
+  <si>
+    <t>Customs + Air + General warehouse</t>
+  </si>
+  <si>
+    <t>COGB</t>
+  </si>
+  <si>
+    <t>Customs + Ocean + General warehouse</t>
+  </si>
+  <si>
+    <t>CGBB</t>
+  </si>
+  <si>
+    <t>Customs + General warehouse</t>
+  </si>
+  <si>
+    <t>TAGB</t>
+  </si>
+  <si>
+    <t>Trucking + Air + General warehouse</t>
+  </si>
+  <si>
+    <t>TOGB</t>
+  </si>
+  <si>
+    <t>Trucking + Ocean + General warehouse</t>
+  </si>
+  <si>
+    <t>TGBB</t>
+  </si>
+  <si>
+    <t>Trucking + General warehouse</t>
+  </si>
+  <si>
+    <t>GBBB</t>
+  </si>
+  <si>
+    <t>General warehouse Only</t>
+  </si>
+  <si>
+    <t>AGBB</t>
+  </si>
+  <si>
+    <t>Air + General warehouse</t>
+  </si>
+  <si>
+    <t>OGBB</t>
+  </si>
+  <si>
+    <t>Ocean + General warehouse</t>
+  </si>
+  <si>
+    <t>CBTG</t>
+  </si>
+  <si>
+    <t>Cross-Border + General warehouse</t>
+  </si>
+  <si>
+    <t>FGBB</t>
+  </si>
+  <si>
+    <t>Booking Agent + General warehouse</t>
+  </si>
+  <si>
+    <t>FTGB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Truck + General warehouse</t>
+  </si>
+  <si>
+    <t>FCGB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + General warehouse</t>
+  </si>
+  <si>
+    <t>FCTG</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + Truck + General warehouse</t>
+  </si>
+  <si>
+    <t>TTTB</t>
+  </si>
+  <si>
+    <t>Truck Sea Truck</t>
+  </si>
+  <si>
+    <t>TTBB</t>
+  </si>
+  <si>
+    <t>Truck Air Truck</t>
+  </si>
+  <si>
+    <t>AECO</t>
+  </si>
+  <si>
+    <t>CO only</t>
+  </si>
+  <si>
+    <t>DECO</t>
+  </si>
+  <si>
+    <t>OEFCLCO</t>
+  </si>
+  <si>
+    <t>OELCLCO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]d/mmm/yy;@"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;\-#,##0.00;\-"/>
     <numFmt numFmtId="168" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="169" formatCode="[$-1010409]d/m/yyyy\ h:mm\ AM/PM;@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1073,8 +1731,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1116,8 +1791,26 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1194,6 +1887,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1203,7 +1907,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1436,13 +2140,55 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="9" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="9" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1452,7 +2198,17 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
     <cellStyle name="標準_1問題1シートBlank" xfId="4" xr:uid="{A683D387-F1ED-42C3-928D-68831043DFA8}"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1554,8 +2310,8 @@
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>399443</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>393093</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>44338</xdr:rowOff>
     </xdr:to>
@@ -3301,16 +4057,16 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="M3:M707">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$M3="Low Load"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>$M3="Balanced"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$M3="High Load"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>$M3="Overload"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5389,6 +6145,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:O75" xr:uid="{71AC7A06-A2E4-4CC8-9045-1D086ED83B34}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5632,7 +6389,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3:B9">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6084,13 +6841,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3:B4">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:B16">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6710,15 +7467,979 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AD11BBA-69FC-4664-9019-7BC48CC71163}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B131"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="84" customFormat="1">
-      <c r="A1" s="84" t="s">
+    <row r="1" spans="1:2" s="83" customFormat="1">
+      <c r="A1" s="83" t="s">
         <v>311</v>
       </c>
     </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="86" t="s">
+        <v>312</v>
+      </c>
+      <c r="B9" s="87"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="88" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="88" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="88" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="88" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="89" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="89"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="89" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="89"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="89"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="88" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="88" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="88" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="88" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="88" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="88" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="90" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="90" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="90" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="90" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="91" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="91" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="90" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="90" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="90" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="92" t="s">
+        <v>326</v>
+      </c>
+      <c r="B28" s="93"/>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="94" t="s">
+        <v>327</v>
+      </c>
+      <c r="B29" s="94" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="94" t="s">
+        <v>329</v>
+      </c>
+      <c r="B30" s="94" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="94" t="s">
+        <v>331</v>
+      </c>
+      <c r="B31" s="94" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="94" t="s">
+        <v>333</v>
+      </c>
+      <c r="B32" s="94" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="94" t="s">
+        <v>335</v>
+      </c>
+      <c r="B33" s="94" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="94" t="s">
+        <v>337</v>
+      </c>
+      <c r="B34" s="94" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="94" t="s">
+        <v>339</v>
+      </c>
+      <c r="B35" s="94" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="94" t="s">
+        <v>341</v>
+      </c>
+      <c r="B36" s="94" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="94" t="s">
+        <v>343</v>
+      </c>
+      <c r="B37" s="94" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="94" t="s">
+        <v>345</v>
+      </c>
+      <c r="B38" s="94" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="94" t="s">
+        <v>347</v>
+      </c>
+      <c r="B39" s="94" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="94" t="s">
+        <v>349</v>
+      </c>
+      <c r="B40" s="94" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="94" t="s">
+        <v>351</v>
+      </c>
+      <c r="B41" s="94" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="94" t="s">
+        <v>353</v>
+      </c>
+      <c r="B42" s="94" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="94" t="s">
+        <v>355</v>
+      </c>
+      <c r="B43" s="94" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="94" t="s">
+        <v>357</v>
+      </c>
+      <c r="B44" s="94" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="94" t="s">
+        <v>359</v>
+      </c>
+      <c r="B45" s="94" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="94" t="s">
+        <v>361</v>
+      </c>
+      <c r="B46" s="94" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="94" t="s">
+        <v>363</v>
+      </c>
+      <c r="B47" s="94" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="94" t="s">
+        <v>365</v>
+      </c>
+      <c r="B48" s="94" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="94" t="s">
+        <v>367</v>
+      </c>
+      <c r="B49" s="94" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="94" t="s">
+        <v>369</v>
+      </c>
+      <c r="B50" s="94" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="94" t="s">
+        <v>371</v>
+      </c>
+      <c r="B51" s="94" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="94" t="s">
+        <v>373</v>
+      </c>
+      <c r="B52" s="94" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="94" t="s">
+        <v>375</v>
+      </c>
+      <c r="B53" s="94" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="94" t="s">
+        <v>377</v>
+      </c>
+      <c r="B54" s="94" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="94" t="s">
+        <v>379</v>
+      </c>
+      <c r="B55" s="94" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="94" t="s">
+        <v>381</v>
+      </c>
+      <c r="B56" s="94" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="94" t="s">
+        <v>383</v>
+      </c>
+      <c r="B57" s="94" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="94" t="s">
+        <v>385</v>
+      </c>
+      <c r="B58" s="94" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="94" t="s">
+        <v>387</v>
+      </c>
+      <c r="B59" s="94" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="94" t="s">
+        <v>389</v>
+      </c>
+      <c r="B60" s="94" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="94" t="s">
+        <v>391</v>
+      </c>
+      <c r="B61" s="94" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="94" t="s">
+        <v>393</v>
+      </c>
+      <c r="B62" s="94" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="94" t="s">
+        <v>395</v>
+      </c>
+      <c r="B63" s="94" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="94" t="s">
+        <v>397</v>
+      </c>
+      <c r="B64" s="94" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="94" t="s">
+        <v>399</v>
+      </c>
+      <c r="B65" s="94" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="94" t="s">
+        <v>401</v>
+      </c>
+      <c r="B66" s="94" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="94" t="s">
+        <v>403</v>
+      </c>
+      <c r="B67" s="94" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="94" t="s">
+        <v>405</v>
+      </c>
+      <c r="B68" s="94" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="94" t="s">
+        <v>407</v>
+      </c>
+      <c r="B69" s="94" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="94" t="s">
+        <v>409</v>
+      </c>
+      <c r="B70" s="94" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="94" t="s">
+        <v>411</v>
+      </c>
+      <c r="B71" s="94" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="94" t="s">
+        <v>413</v>
+      </c>
+      <c r="B72" s="94" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="94" t="s">
+        <v>415</v>
+      </c>
+      <c r="B73" s="94" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="94" t="s">
+        <v>417</v>
+      </c>
+      <c r="B74" s="94" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="94" t="s">
+        <v>419</v>
+      </c>
+      <c r="B75" s="94" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="94" t="s">
+        <v>421</v>
+      </c>
+      <c r="B76" s="94" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="95" t="s">
+        <v>423</v>
+      </c>
+      <c r="B77" s="95" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="94" t="s">
+        <v>425</v>
+      </c>
+      <c r="B78" s="94" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="94" t="s">
+        <v>427</v>
+      </c>
+      <c r="B79" s="94" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="94" t="s">
+        <v>429</v>
+      </c>
+      <c r="B80" s="94" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="95" t="s">
+        <v>431</v>
+      </c>
+      <c r="B81" s="95" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="96" t="s">
+        <v>433</v>
+      </c>
+      <c r="B82" s="94" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="96" t="s">
+        <v>435</v>
+      </c>
+      <c r="B83" s="94" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="96" t="s">
+        <v>437</v>
+      </c>
+      <c r="B84" s="94" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="96" t="s">
+        <v>439</v>
+      </c>
+      <c r="B85" s="94" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="96" t="s">
+        <v>441</v>
+      </c>
+      <c r="B86" s="94" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="96" t="s">
+        <v>443</v>
+      </c>
+      <c r="B87" s="94" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="96" t="s">
+        <v>445</v>
+      </c>
+      <c r="B88" s="94" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="96" t="s">
+        <v>447</v>
+      </c>
+      <c r="B89" s="94" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="96" t="s">
+        <v>449</v>
+      </c>
+      <c r="B90" s="94" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="96" t="s">
+        <v>451</v>
+      </c>
+      <c r="B91" s="95" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="95" t="s">
+        <v>453</v>
+      </c>
+      <c r="B92" s="95" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="95" t="s">
+        <v>455</v>
+      </c>
+      <c r="B93" s="95" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="95" t="s">
+        <v>457</v>
+      </c>
+      <c r="B94" s="95" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="95" t="s">
+        <v>459</v>
+      </c>
+      <c r="B95" s="95" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="95" t="s">
+        <v>461</v>
+      </c>
+      <c r="B96" s="95" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="95" t="s">
+        <v>463</v>
+      </c>
+      <c r="B97" s="95" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="95" t="s">
+        <v>465</v>
+      </c>
+      <c r="B98" s="95" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="95" t="s">
+        <v>467</v>
+      </c>
+      <c r="B99" s="95" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="95" t="s">
+        <v>469</v>
+      </c>
+      <c r="B100" s="95" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="95" t="s">
+        <v>471</v>
+      </c>
+      <c r="B101" s="95" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="95" t="s">
+        <v>473</v>
+      </c>
+      <c r="B102" s="95" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="95" t="s">
+        <v>475</v>
+      </c>
+      <c r="B103" s="95" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="95" t="s">
+        <v>477</v>
+      </c>
+      <c r="B104" s="95" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="95" t="s">
+        <v>479</v>
+      </c>
+      <c r="B105" s="95" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="95" t="s">
+        <v>481</v>
+      </c>
+      <c r="B106" s="95" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="95" t="s">
+        <v>483</v>
+      </c>
+      <c r="B107" s="95" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="95" t="s">
+        <v>485</v>
+      </c>
+      <c r="B108" s="95" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="95" t="s">
+        <v>487</v>
+      </c>
+      <c r="B109" s="95" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="95" t="s">
+        <v>489</v>
+      </c>
+      <c r="B110" s="95" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="95" t="s">
+        <v>491</v>
+      </c>
+      <c r="B111" s="95" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="95" t="s">
+        <v>493</v>
+      </c>
+      <c r="B112" s="95" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="95" t="s">
+        <v>495</v>
+      </c>
+      <c r="B113" s="95" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="95" t="s">
+        <v>497</v>
+      </c>
+      <c r="B114" s="95" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="95" t="s">
+        <v>499</v>
+      </c>
+      <c r="B115" s="95" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="95" t="s">
+        <v>501</v>
+      </c>
+      <c r="B116" s="95" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="95" t="s">
+        <v>503</v>
+      </c>
+      <c r="B117" s="95" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="95" t="s">
+        <v>505</v>
+      </c>
+      <c r="B118" s="95" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="95" t="s">
+        <v>507</v>
+      </c>
+      <c r="B119" s="95" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="95" t="s">
+        <v>509</v>
+      </c>
+      <c r="B120" s="95" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="95" t="s">
+        <v>511</v>
+      </c>
+      <c r="B121" s="95" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="95" t="s">
+        <v>513</v>
+      </c>
+      <c r="B122" s="95" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="95" t="s">
+        <v>515</v>
+      </c>
+      <c r="B123" s="95" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="95" t="s">
+        <v>517</v>
+      </c>
+      <c r="B124" s="95" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="95" t="s">
+        <v>519</v>
+      </c>
+      <c r="B125" s="95" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="95" t="s">
+        <v>521</v>
+      </c>
+      <c r="B126" s="95" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="95" t="s">
+        <v>523</v>
+      </c>
+      <c r="B127" s="95" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="94" t="s">
+        <v>525</v>
+      </c>
+      <c r="B128" s="97" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="95" t="s">
+        <v>527</v>
+      </c>
+      <c r="B129" s="97" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="95" t="s">
+        <v>528</v>
+      </c>
+      <c r="B130" s="97" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="95" t="s">
+        <v>529</v>
+      </c>
+      <c r="B131" s="97" t="s">
+        <v>526</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A128">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -6743,8 +8464,8 @@
       <c r="A1" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
     </row>
     <row r="2" spans="1:14" s="33" customFormat="1" ht="52" customHeight="1">
       <c r="A2" s="31" t="s">
@@ -6823,9 +8544,9 @@
       </c>
       <c r="M3" s="76">
         <f>IF(L3="","",IFERROR(L3/SUMIFS($L:$L,$A:$A,A3,$B:$B,B3),""))</f>
-        <v>8.1037682731007449E-2</v>
-      </c>
-      <c r="N3" s="83"/>
+        <v>7.6964973608896717E-2</v>
+      </c>
+      <c r="N3" s="82"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="34" t="s">
@@ -6862,8 +8583,8 @@
         <v>5849</v>
       </c>
       <c r="M4" s="76">
-        <f t="shared" ref="M3:M19" si="1">IF(L4="","",IFERROR(L4/SUMIFS($L:$L,$A:$A,A4,$B:$B,B4),""))</f>
-        <v>6.0986799574583445E-2</v>
+        <f t="shared" ref="M4:M19" si="1">IF(L4="","",IFERROR(L4/SUMIFS($L:$L,$A:$A,A4,$B:$B,B4),""))</f>
+        <v>5.7921787266911599E-2</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -6902,7 +8623,7 @@
       </c>
       <c r="M5" s="76">
         <f t="shared" si="1"/>
-        <v>7.0652513919879881E-2</v>
+        <v>6.7101732008991791E-2</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -6941,7 +8662,7 @@
       </c>
       <c r="M6" s="76">
         <f t="shared" si="1"/>
-        <v>2.727670844368444E-2</v>
+        <v>2.5905863479268376E-2</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -6969,8 +8690,8 @@
       <c r="H7" s="37">
         <v>1310</v>
       </c>
-      <c r="I7" s="37">
-        <v>-5075</v>
+      <c r="I7" s="85">
+        <v>0</v>
       </c>
       <c r="J7" s="37">
         <v>10</v>
@@ -6980,11 +8701,14 @@
       </c>
       <c r="L7" s="38">
         <f t="shared" si="0"/>
-        <v>24384</v>
+        <v>29459</v>
       </c>
       <c r="M7" s="76">
         <f t="shared" si="1"/>
-        <v>0.25424895209893023</v>
+        <v>0.29172814687911586</v>
+      </c>
+      <c r="N7" s="98">
+        <v>-5075</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7023,7 +8747,7 @@
       </c>
       <c r="M8" s="76">
         <f t="shared" si="1"/>
-        <v>0.4835672429253644</v>
+        <v>0.45926461413533237</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7058,7 +8782,7 @@
       </c>
       <c r="M9" s="76">
         <f t="shared" si="1"/>
-        <v>2.2230100306550163E-2</v>
+        <v>2.111288262148325E-2</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7097,7 +8821,7 @@
       </c>
       <c r="M10" s="76">
         <f t="shared" si="1"/>
-        <v>7.9965140130299386E-2</v>
+        <v>7.5746745728926521E-2</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7136,7 +8860,7 @@
       </c>
       <c r="M11" s="76">
         <f t="shared" si="1"/>
-        <v>5.0291738848561501E-2</v>
+        <v>4.7638702922551873E-2</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7175,7 +8899,7 @@
       </c>
       <c r="M12" s="76">
         <f t="shared" si="1"/>
-        <v>7.4566111530327023E-2</v>
+        <v>7.0632531636649176E-2</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7214,7 +8938,7 @@
       </c>
       <c r="M13" s="76">
         <f t="shared" si="1"/>
-        <v>2.7080167072302347E-2</v>
+        <v>2.5651609265989469E-2</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7242,8 +8966,8 @@
       <c r="H14" s="37">
         <v>1351</v>
       </c>
-      <c r="I14" s="37">
-        <v>-5240</v>
+      <c r="I14" s="85">
+        <v>0</v>
       </c>
       <c r="J14" s="37">
         <v>12</v>
@@ -7253,11 +8977,14 @@
       </c>
       <c r="L14" s="38">
         <f t="shared" si="0"/>
-        <v>25945</v>
+        <v>31185</v>
       </c>
       <c r="M14" s="76">
         <f t="shared" si="1"/>
-        <v>0.2757436949336281</v>
+        <v>0.31395032769226122</v>
+      </c>
+      <c r="N14" s="98">
+        <v>-5240</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7296,7 +9023,7 @@
       </c>
       <c r="M15" s="76">
         <f t="shared" si="1"/>
-        <v>0.46817442688461169</v>
+        <v>0.44347686019470256</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7331,7 +9058,7 @@
       </c>
       <c r="M16" s="76">
         <f t="shared" si="1"/>
-        <v>2.4178720600269953E-2</v>
+        <v>2.2903222558919169E-2</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -8166,7 +9893,7 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
+++ b/TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nykgroup-my.sharepoint.com/personal/nguyenbich_ngoc_nykgroup_com/Documents/CS standard time_Claude/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="985" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D2C4F31-FA0F-4217-8291-878E0A1E0CE8}"/>
+  <xr:revisionPtr revIDLastSave="988" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ADF3FCF-9003-4CC2-81AC-9BA2A2CFDB69}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="745" activeTab="1" xr2:uid="{E21F554E-3F05-4DDC-8BE4-80952248A30F}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="531">
   <si>
     <t>Total</t>
   </si>
@@ -1645,6 +1645,9 @@
   </si>
   <si>
     <t>OELCLCO</t>
+  </si>
+  <si>
+    <t>Required FTE = Total Workload (phút) ÷ [FTE_MINUTES × Số tháng có dữ liệu Workload]</t>
   </si>
 </sst>
 </file>
@@ -2144,9 +2147,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2187,6 +2187,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7478,961 +7481,966 @@
         <v>311</v>
       </c>
     </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>530</v>
+      </c>
+    </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="86" t="s">
+      <c r="A9" s="85" t="s">
         <v>312</v>
       </c>
-      <c r="B9" s="87"/>
+      <c r="B9" s="86"/>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="88" t="s">
+      <c r="A10" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="87" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="88" t="s">
+      <c r="A11" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="88" t="s">
+      <c r="B11" s="87" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="88" t="s">
+      <c r="A12" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="87" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="89" t="s">
+      <c r="A13" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="89"/>
+      <c r="B13" s="88"/>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="89" t="s">
+      <c r="A14" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="89"/>
+      <c r="B14" s="88"/>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="89" t="s">
+      <c r="A15" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="89"/>
+      <c r="B15" s="88"/>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="88" t="s">
+      <c r="B16" s="87" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="88" t="s">
+      <c r="A17" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="88" t="s">
+      <c r="B17" s="87" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="88" t="s">
+      <c r="A18" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="88" t="s">
+      <c r="B18" s="87" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="88" t="s">
+      <c r="A19" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="88" t="s">
+      <c r="B19" s="87" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="88" t="s">
+      <c r="B20" s="87" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="90" t="s">
+      <c r="B21" s="89" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="89" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="90" t="s">
+      <c r="B22" s="89" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="91" t="s">
+      <c r="A23" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="91" t="s">
+      <c r="B23" s="90" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="90" t="s">
+      <c r="A24" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="90" t="s">
+      <c r="B24" s="89" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="90" t="s">
+      <c r="B25" s="89" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="92" t="s">
+      <c r="A28" s="91" t="s">
         <v>326</v>
       </c>
-      <c r="B28" s="93"/>
+      <c r="B28" s="92"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="94" t="s">
+      <c r="A29" s="93" t="s">
         <v>327</v>
       </c>
-      <c r="B29" s="94" t="s">
+      <c r="B29" s="93" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="94" t="s">
+      <c r="A30" s="93" t="s">
         <v>329</v>
       </c>
-      <c r="B30" s="94" t="s">
+      <c r="B30" s="93" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="94" t="s">
+      <c r="A31" s="93" t="s">
         <v>331</v>
       </c>
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="93" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="94" t="s">
+      <c r="A32" s="93" t="s">
         <v>333</v>
       </c>
-      <c r="B32" s="94" t="s">
+      <c r="B32" s="93" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="94" t="s">
+      <c r="A33" s="93" t="s">
         <v>335</v>
       </c>
-      <c r="B33" s="94" t="s">
+      <c r="B33" s="93" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="94" t="s">
+      <c r="A34" s="93" t="s">
         <v>337</v>
       </c>
-      <c r="B34" s="94" t="s">
+      <c r="B34" s="93" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="94" t="s">
+      <c r="A35" s="93" t="s">
         <v>339</v>
       </c>
-      <c r="B35" s="94" t="s">
+      <c r="B35" s="93" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="94" t="s">
+      <c r="A36" s="93" t="s">
         <v>341</v>
       </c>
-      <c r="B36" s="94" t="s">
+      <c r="B36" s="93" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="94" t="s">
+      <c r="A37" s="93" t="s">
         <v>343</v>
       </c>
-      <c r="B37" s="94" t="s">
+      <c r="B37" s="93" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="94" t="s">
+      <c r="A38" s="93" t="s">
         <v>345</v>
       </c>
-      <c r="B38" s="94" t="s">
+      <c r="B38" s="93" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="94" t="s">
+      <c r="A39" s="93" t="s">
         <v>347</v>
       </c>
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="93" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="94" t="s">
+      <c r="A40" s="93" t="s">
         <v>349</v>
       </c>
-      <c r="B40" s="94" t="s">
+      <c r="B40" s="93" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="94" t="s">
+      <c r="A41" s="93" t="s">
         <v>351</v>
       </c>
-      <c r="B41" s="94" t="s">
+      <c r="B41" s="93" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="94" t="s">
+      <c r="A42" s="93" t="s">
         <v>353</v>
       </c>
-      <c r="B42" s="94" t="s">
+      <c r="B42" s="93" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="94" t="s">
+      <c r="A43" s="93" t="s">
         <v>355</v>
       </c>
-      <c r="B43" s="94" t="s">
+      <c r="B43" s="93" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="94" t="s">
+      <c r="A44" s="93" t="s">
         <v>357</v>
       </c>
-      <c r="B44" s="94" t="s">
+      <c r="B44" s="93" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="94" t="s">
+      <c r="A45" s="93" t="s">
         <v>359</v>
       </c>
-      <c r="B45" s="94" t="s">
+      <c r="B45" s="93" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="94" t="s">
+      <c r="A46" s="93" t="s">
         <v>361</v>
       </c>
-      <c r="B46" s="94" t="s">
+      <c r="B46" s="93" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="94" t="s">
+      <c r="A47" s="93" t="s">
         <v>363</v>
       </c>
-      <c r="B47" s="94" t="s">
+      <c r="B47" s="93" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="94" t="s">
+      <c r="A48" s="93" t="s">
         <v>365</v>
       </c>
-      <c r="B48" s="94" t="s">
+      <c r="B48" s="93" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="94" t="s">
+      <c r="A49" s="93" t="s">
         <v>367</v>
       </c>
-      <c r="B49" s="94" t="s">
+      <c r="B49" s="93" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="94" t="s">
+      <c r="A50" s="93" t="s">
         <v>369</v>
       </c>
-      <c r="B50" s="94" t="s">
+      <c r="B50" s="93" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="94" t="s">
+      <c r="A51" s="93" t="s">
         <v>371</v>
       </c>
-      <c r="B51" s="94" t="s">
+      <c r="B51" s="93" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="94" t="s">
+      <c r="A52" s="93" t="s">
         <v>373</v>
       </c>
-      <c r="B52" s="94" t="s">
+      <c r="B52" s="93" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="94" t="s">
+      <c r="A53" s="93" t="s">
         <v>375</v>
       </c>
-      <c r="B53" s="94" t="s">
+      <c r="B53" s="93" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="94" t="s">
+      <c r="A54" s="93" t="s">
         <v>377</v>
       </c>
-      <c r="B54" s="94" t="s">
+      <c r="B54" s="93" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="94" t="s">
+      <c r="A55" s="93" t="s">
         <v>379</v>
       </c>
-      <c r="B55" s="94" t="s">
+      <c r="B55" s="93" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="94" t="s">
+      <c r="A56" s="93" t="s">
         <v>381</v>
       </c>
-      <c r="B56" s="94" t="s">
+      <c r="B56" s="93" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="94" t="s">
+      <c r="A57" s="93" t="s">
         <v>383</v>
       </c>
-      <c r="B57" s="94" t="s">
+      <c r="B57" s="93" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="94" t="s">
+      <c r="A58" s="93" t="s">
         <v>385</v>
       </c>
-      <c r="B58" s="94" t="s">
+      <c r="B58" s="93" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="94" t="s">
+      <c r="A59" s="93" t="s">
         <v>387</v>
       </c>
-      <c r="B59" s="94" t="s">
+      <c r="B59" s="93" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="94" t="s">
+      <c r="A60" s="93" t="s">
         <v>389</v>
       </c>
-      <c r="B60" s="94" t="s">
+      <c r="B60" s="93" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="94" t="s">
+      <c r="A61" s="93" t="s">
         <v>391</v>
       </c>
-      <c r="B61" s="94" t="s">
+      <c r="B61" s="93" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="94" t="s">
+      <c r="A62" s="93" t="s">
         <v>393</v>
       </c>
-      <c r="B62" s="94" t="s">
+      <c r="B62" s="93" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="94" t="s">
+      <c r="A63" s="93" t="s">
         <v>395</v>
       </c>
-      <c r="B63" s="94" t="s">
+      <c r="B63" s="93" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="94" t="s">
+      <c r="A64" s="93" t="s">
         <v>397</v>
       </c>
-      <c r="B64" s="94" t="s">
+      <c r="B64" s="93" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="94" t="s">
+      <c r="A65" s="93" t="s">
         <v>399</v>
       </c>
-      <c r="B65" s="94" t="s">
+      <c r="B65" s="93" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="94" t="s">
+      <c r="A66" s="93" t="s">
         <v>401</v>
       </c>
-      <c r="B66" s="94" t="s">
+      <c r="B66" s="93" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="94" t="s">
+      <c r="A67" s="93" t="s">
         <v>403</v>
       </c>
-      <c r="B67" s="94" t="s">
+      <c r="B67" s="93" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="94" t="s">
+      <c r="A68" s="93" t="s">
         <v>405</v>
       </c>
-      <c r="B68" s="94" t="s">
+      <c r="B68" s="93" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="94" t="s">
+      <c r="A69" s="93" t="s">
         <v>407</v>
       </c>
-      <c r="B69" s="94" t="s">
+      <c r="B69" s="93" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="94" t="s">
+      <c r="A70" s="93" t="s">
         <v>409</v>
       </c>
-      <c r="B70" s="94" t="s">
+      <c r="B70" s="93" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="94" t="s">
+      <c r="A71" s="93" t="s">
         <v>411</v>
       </c>
-      <c r="B71" s="94" t="s">
+      <c r="B71" s="93" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="94" t="s">
+      <c r="A72" s="93" t="s">
         <v>413</v>
       </c>
-      <c r="B72" s="94" t="s">
+      <c r="B72" s="93" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="94" t="s">
+      <c r="A73" s="93" t="s">
         <v>415</v>
       </c>
-      <c r="B73" s="94" t="s">
+      <c r="B73" s="93" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="94" t="s">
+      <c r="A74" s="93" t="s">
         <v>417</v>
       </c>
-      <c r="B74" s="94" t="s">
+      <c r="B74" s="93" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="94" t="s">
+      <c r="A75" s="93" t="s">
         <v>419</v>
       </c>
-      <c r="B75" s="94" t="s">
+      <c r="B75" s="93" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="94" t="s">
+      <c r="A76" s="93" t="s">
         <v>421</v>
       </c>
-      <c r="B76" s="94" t="s">
+      <c r="B76" s="93" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="95" t="s">
+      <c r="A77" s="94" t="s">
         <v>423</v>
       </c>
-      <c r="B77" s="95" t="s">
+      <c r="B77" s="94" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="94" t="s">
+      <c r="A78" s="93" t="s">
         <v>425</v>
       </c>
-      <c r="B78" s="94" t="s">
+      <c r="B78" s="93" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="94" t="s">
+      <c r="A79" s="93" t="s">
         <v>427</v>
       </c>
-      <c r="B79" s="94" t="s">
+      <c r="B79" s="93" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="94" t="s">
+      <c r="A80" s="93" t="s">
         <v>429</v>
       </c>
-      <c r="B80" s="94" t="s">
+      <c r="B80" s="93" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="95" t="s">
+      <c r="A81" s="94" t="s">
         <v>431</v>
       </c>
-      <c r="B81" s="95" t="s">
+      <c r="B81" s="94" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="96" t="s">
+      <c r="A82" s="95" t="s">
         <v>433</v>
       </c>
-      <c r="B82" s="94" t="s">
+      <c r="B82" s="93" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="96" t="s">
+      <c r="A83" s="95" t="s">
         <v>435</v>
       </c>
-      <c r="B83" s="94" t="s">
+      <c r="B83" s="93" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="96" t="s">
+      <c r="A84" s="95" t="s">
         <v>437</v>
       </c>
-      <c r="B84" s="94" t="s">
+      <c r="B84" s="93" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="96" t="s">
+      <c r="A85" s="95" t="s">
         <v>439</v>
       </c>
-      <c r="B85" s="94" t="s">
+      <c r="B85" s="93" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="96" t="s">
+      <c r="A86" s="95" t="s">
         <v>441</v>
       </c>
-      <c r="B86" s="94" t="s">
+      <c r="B86" s="93" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="96" t="s">
+      <c r="A87" s="95" t="s">
         <v>443</v>
       </c>
-      <c r="B87" s="94" t="s">
+      <c r="B87" s="93" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="96" t="s">
+      <c r="A88" s="95" t="s">
         <v>445</v>
       </c>
-      <c r="B88" s="94" t="s">
+      <c r="B88" s="93" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="96" t="s">
+      <c r="A89" s="95" t="s">
         <v>447</v>
       </c>
-      <c r="B89" s="94" t="s">
+      <c r="B89" s="93" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="96" t="s">
+      <c r="A90" s="95" t="s">
         <v>449</v>
       </c>
-      <c r="B90" s="94" t="s">
+      <c r="B90" s="93" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="96" t="s">
+      <c r="A91" s="95" t="s">
         <v>451</v>
       </c>
-      <c r="B91" s="95" t="s">
+      <c r="B91" s="94" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="95" t="s">
+      <c r="A92" s="94" t="s">
         <v>453</v>
       </c>
-      <c r="B92" s="95" t="s">
+      <c r="B92" s="94" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="95" t="s">
+      <c r="A93" s="94" t="s">
         <v>455</v>
       </c>
-      <c r="B93" s="95" t="s">
+      <c r="B93" s="94" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="95" t="s">
+      <c r="A94" s="94" t="s">
         <v>457</v>
       </c>
-      <c r="B94" s="95" t="s">
+      <c r="B94" s="94" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="95" t="s">
+      <c r="A95" s="94" t="s">
         <v>459</v>
       </c>
-      <c r="B95" s="95" t="s">
+      <c r="B95" s="94" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="95" t="s">
+      <c r="A96" s="94" t="s">
         <v>461</v>
       </c>
-      <c r="B96" s="95" t="s">
+      <c r="B96" s="94" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="95" t="s">
+      <c r="A97" s="94" t="s">
         <v>463</v>
       </c>
-      <c r="B97" s="95" t="s">
+      <c r="B97" s="94" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="95" t="s">
+      <c r="A98" s="94" t="s">
         <v>465</v>
       </c>
-      <c r="B98" s="95" t="s">
+      <c r="B98" s="94" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="95" t="s">
+      <c r="A99" s="94" t="s">
         <v>467</v>
       </c>
-      <c r="B99" s="95" t="s">
+      <c r="B99" s="94" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="95" t="s">
+      <c r="A100" s="94" t="s">
         <v>469</v>
       </c>
-      <c r="B100" s="95" t="s">
+      <c r="B100" s="94" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="95" t="s">
+      <c r="A101" s="94" t="s">
         <v>471</v>
       </c>
-      <c r="B101" s="95" t="s">
+      <c r="B101" s="94" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="95" t="s">
+      <c r="A102" s="94" t="s">
         <v>473</v>
       </c>
-      <c r="B102" s="95" t="s">
+      <c r="B102" s="94" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="95" t="s">
+      <c r="A103" s="94" t="s">
         <v>475</v>
       </c>
-      <c r="B103" s="95" t="s">
+      <c r="B103" s="94" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="95" t="s">
+      <c r="A104" s="94" t="s">
         <v>477</v>
       </c>
-      <c r="B104" s="95" t="s">
+      <c r="B104" s="94" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="95" t="s">
+      <c r="A105" s="94" t="s">
         <v>479</v>
       </c>
-      <c r="B105" s="95" t="s">
+      <c r="B105" s="94" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="95" t="s">
+      <c r="A106" s="94" t="s">
         <v>481</v>
       </c>
-      <c r="B106" s="95" t="s">
+      <c r="B106" s="94" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="95" t="s">
+      <c r="A107" s="94" t="s">
         <v>483</v>
       </c>
-      <c r="B107" s="95" t="s">
+      <c r="B107" s="94" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="95" t="s">
+      <c r="A108" s="94" t="s">
         <v>485</v>
       </c>
-      <c r="B108" s="95" t="s">
+      <c r="B108" s="94" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="95" t="s">
+      <c r="A109" s="94" t="s">
         <v>487</v>
       </c>
-      <c r="B109" s="95" t="s">
+      <c r="B109" s="94" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="95" t="s">
+      <c r="A110" s="94" t="s">
         <v>489</v>
       </c>
-      <c r="B110" s="95" t="s">
+      <c r="B110" s="94" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="95" t="s">
+      <c r="A111" s="94" t="s">
         <v>491</v>
       </c>
-      <c r="B111" s="95" t="s">
+      <c r="B111" s="94" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="95" t="s">
+      <c r="A112" s="94" t="s">
         <v>493</v>
       </c>
-      <c r="B112" s="95" t="s">
+      <c r="B112" s="94" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="95" t="s">
+      <c r="A113" s="94" t="s">
         <v>495</v>
       </c>
-      <c r="B113" s="95" t="s">
+      <c r="B113" s="94" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="95" t="s">
+      <c r="A114" s="94" t="s">
         <v>497</v>
       </c>
-      <c r="B114" s="95" t="s">
+      <c r="B114" s="94" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="95" t="s">
+      <c r="A115" s="94" t="s">
         <v>499</v>
       </c>
-      <c r="B115" s="95" t="s">
+      <c r="B115" s="94" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="95" t="s">
+      <c r="A116" s="94" t="s">
         <v>501</v>
       </c>
-      <c r="B116" s="95" t="s">
+      <c r="B116" s="94" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="95" t="s">
+      <c r="A117" s="94" t="s">
         <v>503</v>
       </c>
-      <c r="B117" s="95" t="s">
+      <c r="B117" s="94" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="95" t="s">
+      <c r="A118" s="94" t="s">
         <v>505</v>
       </c>
-      <c r="B118" s="95" t="s">
+      <c r="B118" s="94" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="95" t="s">
+      <c r="A119" s="94" t="s">
         <v>507</v>
       </c>
-      <c r="B119" s="95" t="s">
+      <c r="B119" s="94" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="95" t="s">
+      <c r="A120" s="94" t="s">
         <v>509</v>
       </c>
-      <c r="B120" s="95" t="s">
+      <c r="B120" s="94" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="95" t="s">
+      <c r="A121" s="94" t="s">
         <v>511</v>
       </c>
-      <c r="B121" s="95" t="s">
+      <c r="B121" s="94" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="95" t="s">
+      <c r="A122" s="94" t="s">
         <v>513</v>
       </c>
-      <c r="B122" s="95" t="s">
+      <c r="B122" s="94" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="95" t="s">
+      <c r="A123" s="94" t="s">
         <v>515</v>
       </c>
-      <c r="B123" s="95" t="s">
+      <c r="B123" s="94" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="95" t="s">
+      <c r="A124" s="94" t="s">
         <v>517</v>
       </c>
-      <c r="B124" s="95" t="s">
+      <c r="B124" s="94" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="95" t="s">
+      <c r="A125" s="94" t="s">
         <v>519</v>
       </c>
-      <c r="B125" s="95" t="s">
+      <c r="B125" s="94" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="95" t="s">
+      <c r="A126" s="94" t="s">
         <v>521</v>
       </c>
-      <c r="B126" s="95" t="s">
+      <c r="B126" s="94" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="95" t="s">
+      <c r="A127" s="94" t="s">
         <v>523</v>
       </c>
-      <c r="B127" s="95" t="s">
+      <c r="B127" s="94" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="94" t="s">
+      <c r="A128" s="93" t="s">
         <v>525</v>
       </c>
-      <c r="B128" s="97" t="s">
+      <c r="B128" s="96" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="95" t="s">
+      <c r="A129" s="94" t="s">
         <v>527</v>
       </c>
-      <c r="B129" s="97" t="s">
+      <c r="B129" s="96" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="95" t="s">
+      <c r="A130" s="94" t="s">
         <v>528</v>
       </c>
-      <c r="B130" s="97" t="s">
+      <c r="B130" s="96" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="95" t="s">
+      <c r="A131" s="94" t="s">
         <v>529</v>
       </c>
-      <c r="B131" s="97" t="s">
+      <c r="B131" s="96" t="s">
         <v>526</v>
       </c>
     </row>
@@ -8457,15 +8465,16 @@
     <col min="9" max="9" width="12.08984375" style="19" customWidth="1"/>
     <col min="10" max="12" width="10.1796875" style="19" customWidth="1"/>
     <col min="13" max="13" width="11.453125" style="30" customWidth="1"/>
-    <col min="14" max="16384" width="8.7265625" style="19"/>
+    <col min="14" max="14" width="10.6328125" style="19" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.7265625" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
     </row>
     <row r="2" spans="1:14" s="33" customFormat="1" ht="52" customHeight="1">
       <c r="A2" s="31" t="s">
@@ -8690,7 +8699,7 @@
       <c r="H7" s="37">
         <v>1310</v>
       </c>
-      <c r="I7" s="85">
+      <c r="I7" s="84">
         <v>0</v>
       </c>
       <c r="J7" s="37">
@@ -8707,7 +8716,7 @@
         <f t="shared" si="1"/>
         <v>0.29172814687911586</v>
       </c>
-      <c r="N7" s="98">
+      <c r="N7" s="97">
         <v>-5075</v>
       </c>
     </row>
@@ -8966,7 +8975,7 @@
       <c r="H14" s="37">
         <v>1351</v>
       </c>
-      <c r="I14" s="85">
+      <c r="I14" s="84">
         <v>0</v>
       </c>
       <c r="J14" s="37">
@@ -8983,7 +8992,7 @@
         <f t="shared" si="1"/>
         <v>0.31395032769226122</v>
       </c>
-      <c r="N14" s="98">
+      <c r="N14" s="97">
         <v>-5240</v>
       </c>
     </row>
@@ -9061,7 +9070,7 @@
         <v>2.2903222558919169E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:14">
       <c r="A17" s="34" t="s">
         <v>1</v>
       </c>
@@ -9087,8 +9096,12 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17" s="82">
+        <f>SUM(L3:L16)/60</f>
+        <v>3338.5333333333333</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="34" t="s">
         <v>1</v>
       </c>
@@ -9115,7 +9128,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:14">
       <c r="A19" s="34" t="s">
         <v>1</v>
       </c>
@@ -9142,7 +9155,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:14">
       <c r="A20" s="34" t="s">
         <v>1</v>
       </c>
@@ -9169,7 +9182,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:14">
       <c r="A21" s="34" t="s">
         <v>1</v>
       </c>
@@ -9196,7 +9209,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:14">
       <c r="A22" s="34" t="s">
         <v>1</v>
       </c>
@@ -9223,7 +9236,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:14">
       <c r="A23" s="34" t="s">
         <v>1</v>
       </c>
@@ -9250,7 +9263,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:14">
       <c r="A24" s="34" t="s">
         <v>1</v>
       </c>
@@ -9277,7 +9290,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:14">
       <c r="A25" s="34" t="s">
         <v>1</v>
       </c>
@@ -9304,7 +9317,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:14">
       <c r="A26" s="34" t="s">
         <v>1</v>
       </c>
@@ -9331,7 +9344,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:14">
       <c r="A27" s="34" t="s">
         <v>1</v>
       </c>
@@ -9358,7 +9371,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:14">
       <c r="A28" s="34" t="s">
         <v>1</v>
       </c>
@@ -9385,7 +9398,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:14">
       <c r="A29" s="34" t="s">
         <v>1</v>
       </c>
@@ -9412,7 +9425,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:14">
       <c r="A30" s="34" t="s">
         <v>1</v>
       </c>
@@ -9439,7 +9452,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:14">
       <c r="A31" s="34" t="s">
         <v>3</v>
       </c>
@@ -9466,7 +9479,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:14">
       <c r="A32" s="34" t="s">
         <v>3</v>
       </c>

--- a/TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
+++ b/TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nykgroup-my.sharepoint.com/personal/nguyenbich_ngoc_nykgroup_com/Documents/CS standard time_Claude/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="988" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ADF3FCF-9003-4CC2-81AC-9BA2A2CFDB69}"/>
+  <xr:revisionPtr revIDLastSave="991" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{018253C4-8826-4777-BE3F-3ED241B4CC33}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="745" activeTab="1" xr2:uid="{E21F554E-3F05-4DDC-8BE4-80952248A30F}"/>
   </bookViews>
@@ -1910,7 +1910,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2185,9 +2185,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8473,8 +8470,8 @@
       <c r="A1" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:14" s="33" customFormat="1" ht="52" customHeight="1">
       <c r="A2" s="31" t="s">
@@ -8553,7 +8550,7 @@
       </c>
       <c r="M3" s="76">
         <f>IF(L3="","",IFERROR(L3/SUMIFS($L:$L,$A:$A,A3,$B:$B,B3),""))</f>
-        <v>7.6964973608896717E-2</v>
+        <v>8.1037682731007449E-2</v>
       </c>
       <c r="N3" s="82"/>
     </row>
@@ -8593,7 +8590,7 @@
       </c>
       <c r="M4" s="76">
         <f t="shared" ref="M4:M19" si="1">IF(L4="","",IFERROR(L4/SUMIFS($L:$L,$A:$A,A4,$B:$B,B4),""))</f>
-        <v>5.7921787266911599E-2</v>
+        <v>6.0986799574583445E-2</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -8632,7 +8629,7 @@
       </c>
       <c r="M5" s="76">
         <f t="shared" si="1"/>
-        <v>6.7101732008991791E-2</v>
+        <v>7.0652513919879881E-2</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -8671,7 +8668,7 @@
       </c>
       <c r="M6" s="76">
         <f t="shared" si="1"/>
-        <v>2.5905863479268376E-2</v>
+        <v>2.727670844368444E-2</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -8700,7 +8697,7 @@
         <v>1310</v>
       </c>
       <c r="I7" s="84">
-        <v>0</v>
+        <v>-5075</v>
       </c>
       <c r="J7" s="37">
         <v>10</v>
@@ -8710,14 +8707,11 @@
       </c>
       <c r="L7" s="38">
         <f t="shared" si="0"/>
-        <v>29459</v>
+        <v>24384</v>
       </c>
       <c r="M7" s="76">
         <f t="shared" si="1"/>
-        <v>0.29172814687911586</v>
-      </c>
-      <c r="N7" s="97">
-        <v>-5075</v>
+        <v>0.25424895209893023</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -8756,7 +8750,7 @@
       </c>
       <c r="M8" s="76">
         <f t="shared" si="1"/>
-        <v>0.45926461413533237</v>
+        <v>0.4835672429253644</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8791,7 +8785,7 @@
       </c>
       <c r="M9" s="76">
         <f t="shared" si="1"/>
-        <v>2.111288262148325E-2</v>
+        <v>2.2230100306550163E-2</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8830,7 +8824,7 @@
       </c>
       <c r="M10" s="76">
         <f t="shared" si="1"/>
-        <v>7.5746745728926521E-2</v>
+        <v>7.9965140130299386E-2</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8869,7 +8863,7 @@
       </c>
       <c r="M11" s="76">
         <f t="shared" si="1"/>
-        <v>4.7638702922551873E-2</v>
+        <v>5.0291738848561501E-2</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8908,7 +8902,7 @@
       </c>
       <c r="M12" s="76">
         <f t="shared" si="1"/>
-        <v>7.0632531636649176E-2</v>
+        <v>7.4566111530327023E-2</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8947,7 +8941,7 @@
       </c>
       <c r="M13" s="76">
         <f t="shared" si="1"/>
-        <v>2.5651609265989469E-2</v>
+        <v>2.7080167072302347E-2</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8976,7 +8970,7 @@
         <v>1351</v>
       </c>
       <c r="I14" s="84">
-        <v>0</v>
+        <v>-5240</v>
       </c>
       <c r="J14" s="37">
         <v>12</v>
@@ -8986,14 +8980,11 @@
       </c>
       <c r="L14" s="38">
         <f t="shared" si="0"/>
-        <v>31185</v>
+        <v>25945</v>
       </c>
       <c r="M14" s="76">
         <f t="shared" si="1"/>
-        <v>0.31395032769226122</v>
-      </c>
-      <c r="N14" s="97">
-        <v>-5240</v>
+        <v>0.2757436949336281</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -9032,7 +9023,7 @@
       </c>
       <c r="M15" s="76">
         <f t="shared" si="1"/>
-        <v>0.44347686019470256</v>
+        <v>0.46817442688461169</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -9067,10 +9058,10 @@
       </c>
       <c r="M16" s="76">
         <f t="shared" si="1"/>
-        <v>2.2903222558919169E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>2.4178720600269953E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="34" t="s">
         <v>1</v>
       </c>
@@ -9096,12 +9087,8 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N17" s="82">
-        <f>SUM(L3:L16)/60</f>
-        <v>3338.5333333333333</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="34" t="s">
         <v>1</v>
       </c>
@@ -9128,7 +9115,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:13">
       <c r="A19" s="34" t="s">
         <v>1</v>
       </c>
@@ -9155,7 +9142,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:13">
       <c r="A20" s="34" t="s">
         <v>1</v>
       </c>
@@ -9182,7 +9169,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:13">
       <c r="A21" s="34" t="s">
         <v>1</v>
       </c>
@@ -9209,7 +9196,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:13">
       <c r="A22" s="34" t="s">
         <v>1</v>
       </c>
@@ -9236,7 +9223,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:13">
       <c r="A23" s="34" t="s">
         <v>1</v>
       </c>
@@ -9263,7 +9250,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:13">
       <c r="A24" s="34" t="s">
         <v>1</v>
       </c>
@@ -9290,7 +9277,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:13">
       <c r="A25" s="34" t="s">
         <v>1</v>
       </c>
@@ -9317,7 +9304,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:13">
       <c r="A26" s="34" t="s">
         <v>1</v>
       </c>
@@ -9344,7 +9331,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:13">
       <c r="A27" s="34" t="s">
         <v>1</v>
       </c>
@@ -9371,7 +9358,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:13">
       <c r="A28" s="34" t="s">
         <v>1</v>
       </c>
@@ -9398,7 +9385,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:13">
       <c r="A29" s="34" t="s">
         <v>1</v>
       </c>
@@ -9425,7 +9412,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:13">
       <c r="A30" s="34" t="s">
         <v>1</v>
       </c>
@@ -9452,7 +9439,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:13">
       <c r="A31" s="34" t="s">
         <v>3</v>
       </c>
@@ -9479,7 +9466,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:13">
       <c r="A32" s="34" t="s">
         <v>3</v>
       </c>

--- a/TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
+++ b/TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nykgroup-my.sharepoint.com/personal/nguyenbich_ngoc_nykgroup_com/Documents/CS standard time_Claude/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="991" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{018253C4-8826-4777-BE3F-3ED241B4CC33}"/>
+  <xr:revisionPtr revIDLastSave="1000" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC4B07A0-C13E-4C46-917C-21F25B2CE420}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="745" activeTab="1" xr2:uid="{E21F554E-3F05-4DDC-8BE4-80952248A30F}"/>
   </bookViews>
@@ -1910,7 +1910,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2134,9 +2134,6 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2185,6 +2182,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4096,10 +4099,10 @@
       <c r="B2" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="81" t="s">
+      <c r="D2" s="80" t="s">
         <v>43</v>
       </c>
       <c r="E2" s="44" t="s">
@@ -6171,10 +6174,10 @@
       <c r="B2" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="81" t="s">
+      <c r="D2" s="80" t="s">
         <v>43</v>
       </c>
       <c r="E2" s="44" t="s">
@@ -6415,10 +6418,10 @@
       <c r="B2" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="81" t="s">
+      <c r="D2" s="80" t="s">
         <v>43</v>
       </c>
       <c r="E2" s="44" t="s">
@@ -6886,10 +6889,10 @@
       <c r="E2" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="F2" s="81" t="s">
+      <c r="F2" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="81" t="s">
+      <c r="G2" s="80" t="s">
         <v>43</v>
       </c>
       <c r="H2" s="44" t="s">
@@ -7473,8 +7476,8 @@
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="83" customFormat="1">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:2" s="82" customFormat="1">
+      <c r="A1" s="82" t="s">
         <v>311</v>
       </c>
     </row>
@@ -7484,960 +7487,960 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="84" t="s">
         <v>312</v>
       </c>
-      <c r="B9" s="86"/>
+      <c r="B9" s="85"/>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="86" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="86" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="87" t="s">
+      <c r="B12" s="86" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="88" t="s">
+      <c r="A13" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="88"/>
+      <c r="B13" s="87"/>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="88"/>
+      <c r="B14" s="87"/>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="88"/>
+      <c r="B15" s="87"/>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="87" t="s">
+      <c r="A16" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="87" t="s">
+      <c r="B16" s="86" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="87" t="s">
+      <c r="A17" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="86" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="87" t="s">
+      <c r="A18" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="87" t="s">
+      <c r="B18" s="86" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="87" t="s">
+      <c r="A19" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="86" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="87" t="s">
+      <c r="B20" s="86" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="89" t="s">
+      <c r="A21" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="88" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="89" t="s">
+      <c r="A22" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="89" t="s">
+      <c r="B22" s="88" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="89" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="90" t="s">
+      <c r="B23" s="89" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="89" t="s">
+      <c r="A24" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="89" t="s">
+      <c r="B24" s="88" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="89" t="s">
+      <c r="A25" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="89" t="s">
+      <c r="B25" s="88" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="91" t="s">
+      <c r="A28" s="90" t="s">
         <v>326</v>
       </c>
-      <c r="B28" s="92"/>
+      <c r="B28" s="91"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="93" t="s">
+      <c r="A29" s="92" t="s">
         <v>327</v>
       </c>
-      <c r="B29" s="93" t="s">
+      <c r="B29" s="92" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="93" t="s">
+      <c r="A30" s="92" t="s">
         <v>329</v>
       </c>
-      <c r="B30" s="93" t="s">
+      <c r="B30" s="92" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="93" t="s">
+      <c r="A31" s="92" t="s">
         <v>331</v>
       </c>
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="92" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="93" t="s">
+      <c r="A32" s="92" t="s">
         <v>333</v>
       </c>
-      <c r="B32" s="93" t="s">
+      <c r="B32" s="92" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="93" t="s">
+      <c r="A33" s="92" t="s">
         <v>335</v>
       </c>
-      <c r="B33" s="93" t="s">
+      <c r="B33" s="92" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="93" t="s">
+      <c r="A34" s="92" t="s">
         <v>337</v>
       </c>
-      <c r="B34" s="93" t="s">
+      <c r="B34" s="92" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="93" t="s">
+      <c r="A35" s="92" t="s">
         <v>339</v>
       </c>
-      <c r="B35" s="93" t="s">
+      <c r="B35" s="92" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="93" t="s">
+      <c r="A36" s="92" t="s">
         <v>341</v>
       </c>
-      <c r="B36" s="93" t="s">
+      <c r="B36" s="92" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="93" t="s">
+      <c r="A37" s="92" t="s">
         <v>343</v>
       </c>
-      <c r="B37" s="93" t="s">
+      <c r="B37" s="92" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="93" t="s">
+      <c r="A38" s="92" t="s">
         <v>345</v>
       </c>
-      <c r="B38" s="93" t="s">
+      <c r="B38" s="92" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="93" t="s">
+      <c r="A39" s="92" t="s">
         <v>347</v>
       </c>
-      <c r="B39" s="93" t="s">
+      <c r="B39" s="92" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="93" t="s">
+      <c r="A40" s="92" t="s">
         <v>349</v>
       </c>
-      <c r="B40" s="93" t="s">
+      <c r="B40" s="92" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="93" t="s">
+      <c r="A41" s="92" t="s">
         <v>351</v>
       </c>
-      <c r="B41" s="93" t="s">
+      <c r="B41" s="92" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="93" t="s">
+      <c r="A42" s="92" t="s">
         <v>353</v>
       </c>
-      <c r="B42" s="93" t="s">
+      <c r="B42" s="92" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="93" t="s">
+      <c r="A43" s="92" t="s">
         <v>355</v>
       </c>
-      <c r="B43" s="93" t="s">
+      <c r="B43" s="92" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="92" t="s">
         <v>357</v>
       </c>
-      <c r="B44" s="93" t="s">
+      <c r="B44" s="92" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="93" t="s">
+      <c r="A45" s="92" t="s">
         <v>359</v>
       </c>
-      <c r="B45" s="93" t="s">
+      <c r="B45" s="92" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="93" t="s">
+      <c r="A46" s="92" t="s">
         <v>361</v>
       </c>
-      <c r="B46" s="93" t="s">
+      <c r="B46" s="92" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="93" t="s">
+      <c r="A47" s="92" t="s">
         <v>363</v>
       </c>
-      <c r="B47" s="93" t="s">
+      <c r="B47" s="92" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="93" t="s">
+      <c r="A48" s="92" t="s">
         <v>365</v>
       </c>
-      <c r="B48" s="93" t="s">
+      <c r="B48" s="92" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="93" t="s">
+      <c r="A49" s="92" t="s">
         <v>367</v>
       </c>
-      <c r="B49" s="93" t="s">
+      <c r="B49" s="92" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="93" t="s">
+      <c r="A50" s="92" t="s">
         <v>369</v>
       </c>
-      <c r="B50" s="93" t="s">
+      <c r="B50" s="92" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="93" t="s">
+      <c r="A51" s="92" t="s">
         <v>371</v>
       </c>
-      <c r="B51" s="93" t="s">
+      <c r="B51" s="92" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="93" t="s">
+      <c r="A52" s="92" t="s">
         <v>373</v>
       </c>
-      <c r="B52" s="93" t="s">
+      <c r="B52" s="92" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="93" t="s">
+      <c r="A53" s="92" t="s">
         <v>375</v>
       </c>
-      <c r="B53" s="93" t="s">
+      <c r="B53" s="92" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="93" t="s">
+      <c r="A54" s="92" t="s">
         <v>377</v>
       </c>
-      <c r="B54" s="93" t="s">
+      <c r="B54" s="92" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="93" t="s">
+      <c r="A55" s="92" t="s">
         <v>379</v>
       </c>
-      <c r="B55" s="93" t="s">
+      <c r="B55" s="92" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="93" t="s">
+      <c r="A56" s="92" t="s">
         <v>381</v>
       </c>
-      <c r="B56" s="93" t="s">
+      <c r="B56" s="92" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="93" t="s">
+      <c r="A57" s="92" t="s">
         <v>383</v>
       </c>
-      <c r="B57" s="93" t="s">
+      <c r="B57" s="92" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="93" t="s">
+      <c r="A58" s="92" t="s">
         <v>385</v>
       </c>
-      <c r="B58" s="93" t="s">
+      <c r="B58" s="92" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="93" t="s">
+      <c r="A59" s="92" t="s">
         <v>387</v>
       </c>
-      <c r="B59" s="93" t="s">
+      <c r="B59" s="92" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="93" t="s">
+      <c r="A60" s="92" t="s">
         <v>389</v>
       </c>
-      <c r="B60" s="93" t="s">
+      <c r="B60" s="92" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="93" t="s">
+      <c r="A61" s="92" t="s">
         <v>391</v>
       </c>
-      <c r="B61" s="93" t="s">
+      <c r="B61" s="92" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="93" t="s">
+      <c r="A62" s="92" t="s">
         <v>393</v>
       </c>
-      <c r="B62" s="93" t="s">
+      <c r="B62" s="92" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="93" t="s">
+      <c r="A63" s="92" t="s">
         <v>395</v>
       </c>
-      <c r="B63" s="93" t="s">
+      <c r="B63" s="92" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="93" t="s">
+      <c r="A64" s="92" t="s">
         <v>397</v>
       </c>
-      <c r="B64" s="93" t="s">
+      <c r="B64" s="92" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="93" t="s">
+      <c r="A65" s="92" t="s">
         <v>399</v>
       </c>
-      <c r="B65" s="93" t="s">
+      <c r="B65" s="92" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="93" t="s">
+      <c r="A66" s="92" t="s">
         <v>401</v>
       </c>
-      <c r="B66" s="93" t="s">
+      <c r="B66" s="92" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="93" t="s">
+      <c r="A67" s="92" t="s">
         <v>403</v>
       </c>
-      <c r="B67" s="93" t="s">
+      <c r="B67" s="92" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="93" t="s">
+      <c r="A68" s="92" t="s">
         <v>405</v>
       </c>
-      <c r="B68" s="93" t="s">
+      <c r="B68" s="92" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="93" t="s">
+      <c r="A69" s="92" t="s">
         <v>407</v>
       </c>
-      <c r="B69" s="93" t="s">
+      <c r="B69" s="92" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="93" t="s">
+      <c r="A70" s="92" t="s">
         <v>409</v>
       </c>
-      <c r="B70" s="93" t="s">
+      <c r="B70" s="92" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="93" t="s">
+      <c r="A71" s="92" t="s">
         <v>411</v>
       </c>
-      <c r="B71" s="93" t="s">
+      <c r="B71" s="92" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="93" t="s">
+      <c r="A72" s="92" t="s">
         <v>413</v>
       </c>
-      <c r="B72" s="93" t="s">
+      <c r="B72" s="92" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="93" t="s">
+      <c r="A73" s="92" t="s">
         <v>415</v>
       </c>
-      <c r="B73" s="93" t="s">
+      <c r="B73" s="92" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="93" t="s">
+      <c r="A74" s="92" t="s">
         <v>417</v>
       </c>
-      <c r="B74" s="93" t="s">
+      <c r="B74" s="92" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="93" t="s">
+      <c r="A75" s="92" t="s">
         <v>419</v>
       </c>
-      <c r="B75" s="93" t="s">
+      <c r="B75" s="92" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="93" t="s">
+      <c r="A76" s="92" t="s">
         <v>421</v>
       </c>
-      <c r="B76" s="93" t="s">
+      <c r="B76" s="92" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="94" t="s">
+      <c r="A77" s="93" t="s">
         <v>423</v>
       </c>
-      <c r="B77" s="94" t="s">
+      <c r="B77" s="93" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="93" t="s">
+      <c r="A78" s="92" t="s">
         <v>425</v>
       </c>
-      <c r="B78" s="93" t="s">
+      <c r="B78" s="92" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="93" t="s">
+      <c r="A79" s="92" t="s">
         <v>427</v>
       </c>
-      <c r="B79" s="93" t="s">
+      <c r="B79" s="92" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="93" t="s">
+      <c r="A80" s="92" t="s">
         <v>429</v>
       </c>
-      <c r="B80" s="93" t="s">
+      <c r="B80" s="92" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="94" t="s">
+      <c r="A81" s="93" t="s">
         <v>431</v>
       </c>
-      <c r="B81" s="94" t="s">
+      <c r="B81" s="93" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="95" t="s">
+      <c r="A82" s="94" t="s">
         <v>433</v>
       </c>
-      <c r="B82" s="93" t="s">
+      <c r="B82" s="92" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="95" t="s">
+      <c r="A83" s="94" t="s">
         <v>435</v>
       </c>
-      <c r="B83" s="93" t="s">
+      <c r="B83" s="92" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="95" t="s">
+      <c r="A84" s="94" t="s">
         <v>437</v>
       </c>
-      <c r="B84" s="93" t="s">
+      <c r="B84" s="92" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="95" t="s">
+      <c r="A85" s="94" t="s">
         <v>439</v>
       </c>
-      <c r="B85" s="93" t="s">
+      <c r="B85" s="92" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="95" t="s">
+      <c r="A86" s="94" t="s">
         <v>441</v>
       </c>
-      <c r="B86" s="93" t="s">
+      <c r="B86" s="92" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="95" t="s">
+      <c r="A87" s="94" t="s">
         <v>443</v>
       </c>
-      <c r="B87" s="93" t="s">
+      <c r="B87" s="92" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="95" t="s">
+      <c r="A88" s="94" t="s">
         <v>445</v>
       </c>
-      <c r="B88" s="93" t="s">
+      <c r="B88" s="92" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="95" t="s">
+      <c r="A89" s="94" t="s">
         <v>447</v>
       </c>
-      <c r="B89" s="93" t="s">
+      <c r="B89" s="92" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="95" t="s">
+      <c r="A90" s="94" t="s">
         <v>449</v>
       </c>
-      <c r="B90" s="93" t="s">
+      <c r="B90" s="92" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="95" t="s">
+      <c r="A91" s="94" t="s">
         <v>451</v>
       </c>
-      <c r="B91" s="94" t="s">
+      <c r="B91" s="93" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="94" t="s">
+      <c r="A92" s="93" t="s">
         <v>453</v>
       </c>
-      <c r="B92" s="94" t="s">
+      <c r="B92" s="93" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="94" t="s">
+      <c r="A93" s="93" t="s">
         <v>455</v>
       </c>
-      <c r="B93" s="94" t="s">
+      <c r="B93" s="93" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="94" t="s">
+      <c r="A94" s="93" t="s">
         <v>457</v>
       </c>
-      <c r="B94" s="94" t="s">
+      <c r="B94" s="93" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="94" t="s">
+      <c r="A95" s="93" t="s">
         <v>459</v>
       </c>
-      <c r="B95" s="94" t="s">
+      <c r="B95" s="93" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="94" t="s">
+      <c r="A96" s="93" t="s">
         <v>461</v>
       </c>
-      <c r="B96" s="94" t="s">
+      <c r="B96" s="93" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="94" t="s">
+      <c r="A97" s="93" t="s">
         <v>463</v>
       </c>
-      <c r="B97" s="94" t="s">
+      <c r="B97" s="93" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="94" t="s">
+      <c r="A98" s="93" t="s">
         <v>465</v>
       </c>
-      <c r="B98" s="94" t="s">
+      <c r="B98" s="93" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="94" t="s">
+      <c r="A99" s="93" t="s">
         <v>467</v>
       </c>
-      <c r="B99" s="94" t="s">
+      <c r="B99" s="93" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="94" t="s">
+      <c r="A100" s="93" t="s">
         <v>469</v>
       </c>
-      <c r="B100" s="94" t="s">
+      <c r="B100" s="93" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="94" t="s">
+      <c r="A101" s="93" t="s">
         <v>471</v>
       </c>
-      <c r="B101" s="94" t="s">
+      <c r="B101" s="93" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="94" t="s">
+      <c r="A102" s="93" t="s">
         <v>473</v>
       </c>
-      <c r="B102" s="94" t="s">
+      <c r="B102" s="93" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="94" t="s">
+      <c r="A103" s="93" t="s">
         <v>475</v>
       </c>
-      <c r="B103" s="94" t="s">
+      <c r="B103" s="93" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="94" t="s">
+      <c r="A104" s="93" t="s">
         <v>477</v>
       </c>
-      <c r="B104" s="94" t="s">
+      <c r="B104" s="93" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="94" t="s">
+      <c r="A105" s="93" t="s">
         <v>479</v>
       </c>
-      <c r="B105" s="94" t="s">
+      <c r="B105" s="93" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="94" t="s">
+      <c r="A106" s="93" t="s">
         <v>481</v>
       </c>
-      <c r="B106" s="94" t="s">
+      <c r="B106" s="93" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="94" t="s">
+      <c r="A107" s="93" t="s">
         <v>483</v>
       </c>
-      <c r="B107" s="94" t="s">
+      <c r="B107" s="93" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="94" t="s">
+      <c r="A108" s="93" t="s">
         <v>485</v>
       </c>
-      <c r="B108" s="94" t="s">
+      <c r="B108" s="93" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="94" t="s">
+      <c r="A109" s="93" t="s">
         <v>487</v>
       </c>
-      <c r="B109" s="94" t="s">
+      <c r="B109" s="93" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="94" t="s">
+      <c r="A110" s="93" t="s">
         <v>489</v>
       </c>
-      <c r="B110" s="94" t="s">
+      <c r="B110" s="93" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="94" t="s">
+      <c r="A111" s="93" t="s">
         <v>491</v>
       </c>
-      <c r="B111" s="94" t="s">
+      <c r="B111" s="93" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="94" t="s">
+      <c r="A112" s="93" t="s">
         <v>493</v>
       </c>
-      <c r="B112" s="94" t="s">
+      <c r="B112" s="93" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="94" t="s">
+      <c r="A113" s="93" t="s">
         <v>495</v>
       </c>
-      <c r="B113" s="94" t="s">
+      <c r="B113" s="93" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="94" t="s">
+      <c r="A114" s="93" t="s">
         <v>497</v>
       </c>
-      <c r="B114" s="94" t="s">
+      <c r="B114" s="93" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="94" t="s">
+      <c r="A115" s="93" t="s">
         <v>499</v>
       </c>
-      <c r="B115" s="94" t="s">
+      <c r="B115" s="93" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="94" t="s">
+      <c r="A116" s="93" t="s">
         <v>501</v>
       </c>
-      <c r="B116" s="94" t="s">
+      <c r="B116" s="93" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="94" t="s">
+      <c r="A117" s="93" t="s">
         <v>503</v>
       </c>
-      <c r="B117" s="94" t="s">
+      <c r="B117" s="93" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="94" t="s">
+      <c r="A118" s="93" t="s">
         <v>505</v>
       </c>
-      <c r="B118" s="94" t="s">
+      <c r="B118" s="93" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="94" t="s">
+      <c r="A119" s="93" t="s">
         <v>507</v>
       </c>
-      <c r="B119" s="94" t="s">
+      <c r="B119" s="93" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="94" t="s">
+      <c r="A120" s="93" t="s">
         <v>509</v>
       </c>
-      <c r="B120" s="94" t="s">
+      <c r="B120" s="93" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="94" t="s">
+      <c r="A121" s="93" t="s">
         <v>511</v>
       </c>
-      <c r="B121" s="94" t="s">
+      <c r="B121" s="93" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="94" t="s">
+      <c r="A122" s="93" t="s">
         <v>513</v>
       </c>
-      <c r="B122" s="94" t="s">
+      <c r="B122" s="93" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="94" t="s">
+      <c r="A123" s="93" t="s">
         <v>515</v>
       </c>
-      <c r="B123" s="94" t="s">
+      <c r="B123" s="93" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="94" t="s">
+      <c r="A124" s="93" t="s">
         <v>517</v>
       </c>
-      <c r="B124" s="94" t="s">
+      <c r="B124" s="93" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="94" t="s">
+      <c r="A125" s="93" t="s">
         <v>519</v>
       </c>
-      <c r="B125" s="94" t="s">
+      <c r="B125" s="93" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="94" t="s">
+      <c r="A126" s="93" t="s">
         <v>521</v>
       </c>
-      <c r="B126" s="94" t="s">
+      <c r="B126" s="93" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="94" t="s">
+      <c r="A127" s="93" t="s">
         <v>523</v>
       </c>
-      <c r="B127" s="94" t="s">
+      <c r="B127" s="93" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="93" t="s">
+      <c r="A128" s="92" t="s">
         <v>525</v>
       </c>
-      <c r="B128" s="96" t="s">
+      <c r="B128" s="95" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="94" t="s">
+      <c r="A129" s="93" t="s">
         <v>527</v>
       </c>
-      <c r="B129" s="96" t="s">
+      <c r="B129" s="95" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="94" t="s">
+      <c r="A130" s="93" t="s">
         <v>528</v>
       </c>
-      <c r="B130" s="96" t="s">
+      <c r="B130" s="95" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="94" t="s">
+      <c r="A131" s="93" t="s">
         <v>529</v>
       </c>
-      <c r="B131" s="96" t="s">
+      <c r="B131" s="95" t="s">
         <v>526</v>
       </c>
     </row>
@@ -8452,7 +8455,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FE6D61-EE10-43A8-AADB-BC76383CE52B}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="16"/>
   <cols>
     <col min="1" max="2" width="8.7265625" style="19"/>
@@ -8466,14 +8469,14 @@
     <col min="15" max="16384" width="8.7265625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-    </row>
-    <row r="2" spans="1:14" s="33" customFormat="1" ht="52" customHeight="1">
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="2" spans="1:15" s="33" customFormat="1" ht="52" customHeight="1">
       <c r="A2" s="31" t="s">
         <v>5</v>
       </c>
@@ -8514,7 +8517,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
@@ -8552,9 +8555,9 @@
         <f>IF(L3="","",IFERROR(L3/SUMIFS($L:$L,$A:$A,A3,$B:$B,B3),""))</f>
         <v>8.1037682731007449E-2</v>
       </c>
-      <c r="N3" s="82"/>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="N3" s="81"/>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="34" t="s">
         <v>2</v>
       </c>
@@ -8593,7 +8596,7 @@
         <v>6.0986799574583445E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
@@ -8632,7 +8635,7 @@
         <v>7.0652513919879881E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" s="34" t="s">
         <v>2</v>
       </c>
@@ -8671,7 +8674,7 @@
         <v>2.727670844368444E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="34" t="s">
         <v>2</v>
       </c>
@@ -8696,7 +8699,7 @@
       <c r="H7" s="37">
         <v>1310</v>
       </c>
-      <c r="I7" s="84">
+      <c r="I7" s="83">
         <v>-5075</v>
       </c>
       <c r="J7" s="37">
@@ -8714,7 +8717,7 @@
         <v>0.25424895209893023</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="34" t="s">
         <v>2</v>
       </c>
@@ -8753,7 +8756,7 @@
         <v>0.4835672429253644</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="34" t="s">
         <v>2</v>
       </c>
@@ -8788,7 +8791,7 @@
         <v>2.2230100306550163E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="34" t="s">
         <v>2</v>
       </c>
@@ -8827,7 +8830,7 @@
         <v>7.9965140130299386E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="34" t="s">
         <v>2</v>
       </c>
@@ -8866,7 +8869,7 @@
         <v>5.0291738848561501E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="34" t="s">
         <v>2</v>
       </c>
@@ -8905,7 +8908,7 @@
         <v>7.4566111530327023E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="34" t="s">
         <v>2</v>
       </c>
@@ -8944,7 +8947,7 @@
         <v>2.7080167072302347E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" s="34" t="s">
         <v>2</v>
       </c>
@@ -8969,7 +8972,7 @@
       <c r="H14" s="37">
         <v>1351</v>
       </c>
-      <c r="I14" s="84">
+      <c r="I14" s="83">
         <v>-5240</v>
       </c>
       <c r="J14" s="37">
@@ -8987,7 +8990,7 @@
         <v>0.2757436949336281</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15" s="34" t="s">
         <v>2</v>
       </c>
@@ -9026,7 +9029,7 @@
         <v>0.46817442688461169</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="34" t="s">
         <v>2</v>
       </c>
@@ -9060,8 +9063,10 @@
         <f t="shared" si="1"/>
         <v>2.4178720600269953E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" s="81"/>
+      <c r="O16" s="96"/>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="34" t="s">
         <v>1</v>
       </c>
@@ -9079,16 +9084,16 @@
       <c r="I17" s="78"/>
       <c r="J17" s="78"/>
       <c r="K17" s="78"/>
-      <c r="L17" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="80" t="str">
+      <c r="L17" s="97">
+        <v>7524</v>
+      </c>
+      <c r="M17" s="79">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>7.9965140130299386E-2</v>
+      </c>
+      <c r="O17" s="96"/>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="34" t="s">
         <v>1</v>
       </c>
@@ -9106,16 +9111,16 @@
       <c r="I18" s="78"/>
       <c r="J18" s="78"/>
       <c r="K18" s="78"/>
-      <c r="L18" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="80" t="str">
+      <c r="L18" s="97">
+        <v>4732</v>
+      </c>
+      <c r="M18" s="79">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>5.0291738848561501E-2</v>
+      </c>
+      <c r="O18" s="96"/>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="34" t="s">
         <v>1</v>
       </c>
@@ -9133,16 +9138,15 @@
       <c r="I19" s="78"/>
       <c r="J19" s="78"/>
       <c r="K19" s="78"/>
-      <c r="L19" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="80" t="str">
+      <c r="L19" s="97">
+        <v>7016</v>
+      </c>
+      <c r="M19" s="79">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>7.4566111530327023E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="34" t="s">
         <v>1</v>
       </c>
@@ -9160,16 +9164,15 @@
       <c r="I20" s="78"/>
       <c r="J20" s="78"/>
       <c r="K20" s="78"/>
-      <c r="L20" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="80" t="str">
+      <c r="L20" s="97">
+        <v>2548</v>
+      </c>
+      <c r="M20" s="79">
         <f t="shared" ref="M20:M44" si="2">IF(L20="","",IFERROR(L20/SUMIFS($L:$L,$A:$A,A20,$B:$B,B20),""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>2.7080167072302347E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="34" t="s">
         <v>1</v>
       </c>
@@ -9187,16 +9190,15 @@
       <c r="I21" s="78"/>
       <c r="J21" s="78"/>
       <c r="K21" s="78"/>
-      <c r="L21" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="80" t="str">
+      <c r="L21" s="97">
+        <v>25945</v>
+      </c>
+      <c r="M21" s="79">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>0.2757436949336281</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="34" t="s">
         <v>1</v>
       </c>
@@ -9214,16 +9216,15 @@
       <c r="I22" s="78"/>
       <c r="J22" s="78"/>
       <c r="K22" s="78"/>
-      <c r="L22" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="80" t="str">
+      <c r="L22" s="97">
+        <v>44051</v>
+      </c>
+      <c r="M22" s="79">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>0.46817442688461169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="34" t="s">
         <v>1</v>
       </c>
@@ -9241,16 +9242,15 @@
       <c r="I23" s="78"/>
       <c r="J23" s="78"/>
       <c r="K23" s="78"/>
-      <c r="L23" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="80" t="str">
+      <c r="L23" s="97">
+        <v>2275</v>
+      </c>
+      <c r="M23" s="79">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>2.4178720600269953E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="34" t="s">
         <v>1</v>
       </c>
@@ -9277,7 +9277,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:15">
       <c r="A25" s="34" t="s">
         <v>1</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:15">
       <c r="A26" s="34" t="s">
         <v>1</v>
       </c>
@@ -9331,7 +9331,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:15">
       <c r="A27" s="34" t="s">
         <v>1</v>
       </c>
@@ -9358,7 +9358,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:15">
       <c r="A28" s="34" t="s">
         <v>1</v>
       </c>
@@ -9385,7 +9385,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:15">
       <c r="A29" s="34" t="s">
         <v>1</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:15">
       <c r="A30" s="34" t="s">
         <v>1</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:15">
       <c r="A31" s="34" t="s">
         <v>3</v>
       </c>
@@ -9466,7 +9466,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:15">
       <c r="A32" s="34" t="s">
         <v>3</v>
       </c>
@@ -30845,10 +30845,10 @@
       <c r="B2" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="81" t="s">
+      <c r="D2" s="80" t="s">
         <v>43</v>
       </c>
       <c r="E2" s="44" t="s">

--- a/TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
+++ b/TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nykgroup-my.sharepoint.com/personal/nguyenbich_ngoc_nykgroup_com/Documents/CS standard time_Claude/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1000" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC4B07A0-C13E-4C46-917C-21F25B2CE420}"/>
+  <xr:revisionPtr revIDLastSave="1003" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4256E9D1-0F9A-41DC-ABC2-9AC9521A4CA8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="745" activeTab="1" xr2:uid="{E21F554E-3F05-4DDC-8BE4-80952248A30F}"/>
   </bookViews>
@@ -1910,7 +1910,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2186,9 +2186,6 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2201,7 +2198,17 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
     <cellStyle name="標準_1問題1シートBlank" xfId="4" xr:uid="{A683D387-F1ED-42C3-928D-68831043DFA8}"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4060,16 +4067,16 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="M3:M707">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$M3="Low Load"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>$M3="Balanced"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>$M3="High Load"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>$M3="Overload"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6392,7 +6399,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3:B9">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6844,13 +6851,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3:B4">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:B16">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8446,7 +8453,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A128">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8473,8 +8480,8 @@
       <c r="A1" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:15" s="33" customFormat="1" ht="52" customHeight="1">
       <c r="A2" s="31" t="s">
@@ -9084,12 +9091,13 @@
       <c r="I17" s="78"/>
       <c r="J17" s="78"/>
       <c r="K17" s="78"/>
-      <c r="L17" s="97">
-        <v>7524</v>
-      </c>
-      <c r="M17" s="79">
+      <c r="L17" s="38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="79" t="str">
         <f t="shared" si="1"/>
-        <v>7.9965140130299386E-2</v>
+        <v/>
       </c>
       <c r="O17" s="96"/>
     </row>
@@ -9111,12 +9119,13 @@
       <c r="I18" s="78"/>
       <c r="J18" s="78"/>
       <c r="K18" s="78"/>
-      <c r="L18" s="97">
-        <v>4732</v>
-      </c>
-      <c r="M18" s="79">
+      <c r="L18" s="38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="79" t="str">
         <f t="shared" si="1"/>
-        <v>5.0291738848561501E-2</v>
+        <v/>
       </c>
       <c r="O18" s="96"/>
     </row>
@@ -9138,12 +9147,13 @@
       <c r="I19" s="78"/>
       <c r="J19" s="78"/>
       <c r="K19" s="78"/>
-      <c r="L19" s="97">
-        <v>7016</v>
-      </c>
-      <c r="M19" s="79">
+      <c r="L19" s="38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="79" t="str">
         <f t="shared" si="1"/>
-        <v>7.4566111530327023E-2</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -9164,12 +9174,13 @@
       <c r="I20" s="78"/>
       <c r="J20" s="78"/>
       <c r="K20" s="78"/>
-      <c r="L20" s="97">
-        <v>2548</v>
-      </c>
-      <c r="M20" s="79">
+      <c r="L20" s="38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="79" t="str">
         <f t="shared" ref="M20:M44" si="2">IF(L20="","",IFERROR(L20/SUMIFS($L:$L,$A:$A,A20,$B:$B,B20),""))</f>
-        <v>2.7080167072302347E-2</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -9190,12 +9201,13 @@
       <c r="I21" s="78"/>
       <c r="J21" s="78"/>
       <c r="K21" s="78"/>
-      <c r="L21" s="97">
-        <v>25945</v>
-      </c>
-      <c r="M21" s="79">
+      <c r="L21" s="38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="79" t="str">
         <f t="shared" si="2"/>
-        <v>0.2757436949336281</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -9216,12 +9228,13 @@
       <c r="I22" s="78"/>
       <c r="J22" s="78"/>
       <c r="K22" s="78"/>
-      <c r="L22" s="97">
-        <v>44051</v>
-      </c>
-      <c r="M22" s="79">
+      <c r="L22" s="38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="79" t="str">
         <f t="shared" si="2"/>
-        <v>0.46817442688461169</v>
+        <v/>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -9242,12 +9255,13 @@
       <c r="I23" s="78"/>
       <c r="J23" s="78"/>
       <c r="K23" s="78"/>
-      <c r="L23" s="97">
-        <v>2275</v>
-      </c>
-      <c r="M23" s="79">
+      <c r="L23" s="38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="79" t="str">
         <f t="shared" si="2"/>
-        <v>2.4178720600269953E-2</v>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -9892,9 +9906,6 @@
     <mergeCell ref="D1:E1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
